--- a/astro-site/public/dl/food-truck-checklist-templates/03-food-truck-health-inspection-food-safety-checklist.xlsx
+++ b/astro-site/public/dl/food-truck-checklist-templates/03-food-truck-health-inspection-food-safety-checklist.xlsx
@@ -668,7 +668,7 @@
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
     </row>
-    <row r="7" ht="41" customHeight="1">
+    <row r="7" ht="54.5" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Cold temps</t>
@@ -676,7 +676,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Check temperatures on arrival at the vending spot: cold 41 °F or below, frozen 0 °F or below — log reading: ____ °F</t>
+          <t>Check temperatures on arrival at the vending spot: cold 41 °F or below (FDA Food Code 3-501.16); frozen food still frozen (0 °F or below is the common target) — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
